--- a/Modèle-audit-SEO.xlsx
+++ b/Modèle-audit-SEO.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
   <si>
     <t>Catégorie</t>
   </si>
@@ -285,13 +285,34 @@
   </si>
   <si>
     <t>https://stackoverflow.com/questions/25402061/why-do-we-need-multiple-background-color-rules</t>
+  </si>
+  <si>
+    <t>https://webaim.org/standards/wcag/checklist#sc2.4.6</t>
+  </si>
+  <si>
+    <t>A form control does not have a corresponding label.</t>
+  </si>
+  <si>
+    <t>absence de label, ou label non correspondant sur le questionnaire</t>
+  </si>
+  <si>
+    <t>adapter le label au questionnaire</t>
+  </si>
+  <si>
+    <t>accessiblité</t>
+  </si>
+  <si>
+    <t>https://developer.mozilla.org/fr/docs/Web/CSS/@counter-style/speak-as</t>
+  </si>
+  <si>
+    <t>https://developer.mozilla.org/fr/docs/Web/CSS/-ms-filter</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -311,10 +332,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -329,11 +346,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -389,16 +401,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -410,17 +422,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,17 +693,17 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="45" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="8" t="b">
+      <c r="E2" s="7" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -717,7 +723,7 @@
       <c r="D3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="9" t="b">
+      <c r="E3" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -737,7 +743,7 @@
       <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="8" t="b">
+      <c r="E4" s="7" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -757,7 +763,7 @@
       <c r="D5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="9" t="b">
+      <c r="E5" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -777,7 +783,7 @@
       <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="9" t="b">
+      <c r="E6" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -795,7 +801,7 @@
       <c r="D7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="9" t="b">
+      <c r="E7" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -815,7 +821,7 @@
       <c r="D8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="9" t="b">
+      <c r="E8" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -835,7 +841,7 @@
       <c r="D9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="9" t="b">
+      <c r="E9" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="s">
@@ -855,7 +861,7 @@
       <c r="D10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="9" t="b">
+      <c r="E10" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
@@ -875,7 +881,7 @@
       <c r="D11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="9" t="b">
+      <c r="E11" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
@@ -889,13 +895,13 @@
       <c r="B12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="9" t="b">
+      <c r="E12" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -913,12 +919,14 @@
         <v>77</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="8" t="b">
+      <c r="E13" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:26" ht="30" x14ac:dyDescent="0.2">
+      <c r="F13" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -931,10 +939,12 @@
       <c r="D14" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="8" t="b">
+      <c r="E14" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="15" spans="1:26" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
@@ -949,14 +959,33 @@
       <c r="D15" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="9" t="b">
+      <c r="E15" s="8" t="b">
         <v>1</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:26" ht="45" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
     <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
